--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.48154950680933</v>
+        <v>4.303251794856516</v>
       </c>
       <c r="D2" t="n">
-        <v>25.35487217247299</v>
+        <v>4.120166728026861</v>
       </c>
       <c r="E2" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F2" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.8329390353172</v>
+        <v>1.922852593239045</v>
       </c>
       <c r="D3" t="n">
-        <v>13.75781413269333</v>
+        <v>2.235644796562667</v>
       </c>
       <c r="E3" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F3" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.38904445578337</v>
+        <v>2.338219724064798</v>
       </c>
       <c r="D4" t="n">
-        <v>14.69677748332463</v>
+        <v>2.388226341040252</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F4" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.69316866279328</v>
+        <v>5.475139907703909</v>
       </c>
       <c r="D5" t="n">
-        <v>8.480909793429138</v>
+        <v>1.378147841432235</v>
       </c>
       <c r="E5" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F5" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.08140078747697</v>
+        <v>3.588227627965008</v>
       </c>
       <c r="D6" t="n">
-        <v>22.67594756280012</v>
+        <v>3.684841478955019</v>
       </c>
       <c r="E6" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F6" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.38494851494504</v>
+        <v>8.187554133678571</v>
       </c>
       <c r="D7" t="n">
-        <v>50.28304803623796</v>
+        <v>8.170995305888669</v>
       </c>
       <c r="E7" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F7" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>58.91084637404427</v>
+        <v>9.573012535782194</v>
       </c>
       <c r="D8" t="n">
-        <v>58.69415945379219</v>
+        <v>9.537800911241231</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F8" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.45976017278757</v>
+        <v>9.174711028077979</v>
       </c>
       <c r="D9" t="n">
-        <v>56.06085019676151</v>
+        <v>9.109888156973746</v>
       </c>
       <c r="E9" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F9" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.13545654599942</v>
+        <v>5.872011688724905</v>
       </c>
       <c r="D10" t="n">
-        <v>36.61115575689548</v>
+        <v>5.949312810495515</v>
       </c>
       <c r="E10" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F10" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.34514424979935</v>
+        <v>5.581085940592395</v>
       </c>
       <c r="D11" t="n">
-        <v>34.07188602694568</v>
+        <v>5.536681479378672</v>
       </c>
       <c r="E11" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F11" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.65490397956057</v>
+        <v>4.006421896678592</v>
       </c>
       <c r="D12" t="n">
-        <v>24.22764576698249</v>
+        <v>3.936992437134655</v>
       </c>
       <c r="E12" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F12" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.86769050070489</v>
+        <v>1.928499706364544</v>
       </c>
       <c r="D13" t="n">
-        <v>11.58686140043908</v>
+        <v>1.88286497757135</v>
       </c>
       <c r="E13" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F13" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.17143647412072</v>
+        <v>7.015358427044617</v>
       </c>
       <c r="D14" t="n">
-        <v>42.62441283552347</v>
+        <v>6.926467085772565</v>
       </c>
       <c r="E14" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F14" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.19692474419855</v>
+        <v>4.582000270932265</v>
       </c>
       <c r="D15" t="n">
-        <v>27.50285836043021</v>
+        <v>4.469214483569909</v>
       </c>
       <c r="E15" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F15" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>67.61901707492535</v>
+        <v>10.98809027467537</v>
       </c>
       <c r="D16" t="n">
-        <v>67.03986870216757</v>
+        <v>10.89397866410223</v>
       </c>
       <c r="E16" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F16" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.18982903424313</v>
+        <v>6.530847218064509</v>
       </c>
       <c r="D17" t="n">
-        <v>40.3772502756323</v>
+        <v>6.561303169790249</v>
       </c>
       <c r="E17" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F17" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>65.40979853490887</v>
+        <v>10.62909226192269</v>
       </c>
       <c r="D18" t="n">
-        <v>64.77521738043234</v>
+        <v>10.52597282432026</v>
       </c>
       <c r="E18" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F18" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.3627449345107</v>
+        <v>7.858946051857989</v>
       </c>
       <c r="D19" t="n">
-        <v>47.62604573492904</v>
+        <v>7.73923243192597</v>
       </c>
       <c r="E19" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F19" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>12.42315191633066</v>
+        <v>2.018762186403733</v>
       </c>
       <c r="D20" t="n">
-        <v>11.57493692436892</v>
+        <v>1.88092725020995</v>
       </c>
       <c r="E20" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F20" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.62894570720427</v>
+        <v>5.464703677420694</v>
       </c>
       <c r="D21" t="n">
-        <v>34.02069373052242</v>
+        <v>5.528362731209893</v>
       </c>
       <c r="E21" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F21" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>12.63774078294021</v>
+        <v>2.053632877227785</v>
       </c>
       <c r="D22" t="n">
-        <v>12.96955726681699</v>
+        <v>2.10755305585776</v>
       </c>
       <c r="E22" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F22" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>44.17337589250292</v>
+        <v>7.178173582531724</v>
       </c>
       <c r="D23" t="n">
-        <v>43.64079320776652</v>
+        <v>7.09162889626206</v>
       </c>
       <c r="E23" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F23" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>15.832903845007</v>
+        <v>2.572846874813637</v>
       </c>
       <c r="D24" t="n">
-        <v>16.24554865104227</v>
+        <v>2.639901655794369</v>
       </c>
       <c r="E24" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F24" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>18.71523483848795</v>
+        <v>3.041225661254292</v>
       </c>
       <c r="D25" t="n">
-        <v>18.35394350855073</v>
+        <v>2.982515820139494</v>
       </c>
       <c r="E25" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F25" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>32.90994887623646</v>
+        <v>5.347866692388425</v>
       </c>
       <c r="D26" t="n">
-        <v>33.12317272483012</v>
+        <v>5.382515567784894</v>
       </c>
       <c r="E26" t="n">
-        <v>16.87405969972111</v>
+        <v>2.74203470120468</v>
       </c>
       <c r="F26" t="n">
-        <v>17.36456306737715</v>
+        <v>2.821741498448787</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
